--- a/docs/sprint2/audit/audit-Sapronov.xlsx
+++ b/docs/sprint2/audit/audit-Sapronov.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -59,16 +48,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -77,10 +66,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,16 +437,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,20 +468,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Критерій</t>
+          <t>Критерій (моя оцінка)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Опис дефекту (пункт чек-листа, цитата)</t>
+          <t>Пункт чек-листа</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Пропозиція виправлення</t>
+          <t>Що знайдено (запис під час перевірки)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Пропозиція (чернетка)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Результат зведення</t>
         </is>
@@ -520,15 +515,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Посилання на code/modules/shopline/v1/README.md — файлу в репозиторії немає.</t>
+          <t>п. 3</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Вилучити посилання до появи файлу.</t>
+          <t>Посилання на code/modules/shopline/v1/README.md — у репозиторії такого файлу немає.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Прибрати посилання, доки файл не з'явиться.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Відхилено на обговоренні (див. «Спірні»)</t>
         </is>
@@ -542,12 +542,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>2.2 ↔ розд. 6, рядок без ID</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1–2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -557,17 +557,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>п. 2: F-110 «для замовлень від 2000 грн доставка безкоштовна» суперечить BL-60 «0.00 грн, якщо сума після знижки не менша за 1500 грн».</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>F-110: «…вартість доставки визначається за BL-60: 0 грн, якщо сума після знижок не менша за 1500 грн, інакше 120 грн» (поріг 1500 грн після знижки потребує підтвердження замовником).</t>
+          <t>2.2: настільні ОС, вікно від 1280×800. У розділі 6 (рядок без ID після U-20) — «коректно відображається за ширини 375 пікселів». Одна з вимог хибна.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 9 реєстру</t>
+          <t>Або додати мобільні браузери у 2.2, або прибрати вимогу 375 px — питання замовнику.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 13 реєстру</t>
         </is>
       </c>
     </row>
@@ -579,12 +584,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GUI-30</t>
+          <t>BL-10</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -594,17 +599,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>п. 2: GUI-30 «приймає значення від 0 до 100» суперечить BL-10 / BL-40 (qty від 1 до 99): інтерфейс дозволяє кількість, яку модуль відхиляє.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>GUI-30: «…приймає цілі значення від 1 до 99; значення за замовчуванням — 1; на межах кнопка «−» (при 1) або «+» (при 99) неактивна; введене вручну значення поза межами замінюється найближчою межею».</t>
+          <t>Cart.addItem: qty 1…99, інакше IllegalArgumentException. А GUI-30 дозволяє ввести 0…100 — UI пропускає значення, на яких модуль кидає виняток.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 12 реєстру</t>
+          <t>Привести GUI-30 до 1…99.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 12 реєстру (у реєстрі під ID GUI-30)</t>
         </is>
       </c>
     </row>
@@ -631,15 +641,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>п. 1, 5: BL-30 «…не додає окремий рядок, а збільшує кількість у наявному рядку» повторює BL-20 і менш повна (без межі 99).</t>
+          <t>п. 1, 5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BL-30 вилучено із записом у журналі змін; ID не перевикористовується; вимога — BL-20.</t>
+          <t>Дублює BL-20 (той самий sku → +qty до наявного рядка), до того ж без межі 99.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Вилучити BL-30, ID не перевикористовувати.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Прийнято, № 16 реєстру</t>
         </is>
@@ -653,7 +668,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BL-70</t>
+          <t>BL-40</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -663,22 +678,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Повнота</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>п. 4, 5: не описано поведінку для коду, якого немає в довіднику, і для null-аргументів; «причина відмови» не має визначеного переліку значень — юніт-тест не може перевірити причину.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>«…Якщо код не знайдено — непридатний з причиною NOT_FOUND. Причини відмови: NOT_FOUND, INVALID_LENGTH, EXPIRED, ALREADY_USED, INVALID_VALUE; для придатного коду — порожня. Якщо будь-який аргумент null — IllegalArgumentException».</t>
+          <t>changeQty: 1…99 — той самий конфлікт з GUI-30 (0…100), що в С-03.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 7 реєстру</t>
+          <t>Див. С-03.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Об'єднано з С-03 при зведенні → № 12 реєстру</t>
         </is>
       </c>
     </row>
@@ -690,7 +710,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>BL-80</t>
+          <t>BL-60</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -700,22 +720,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Здійсненність</t>
+          <t>Несуперечливість</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>«перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — доступу до даних сторонніх магазинів немає; модуль за 2.3 — бібліотека без зовнішніх залежностей.</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>«…Перед застосуванням одноразового коду система перевіряє, що його не використано в жодному замовленні «ШопЛайн»; використаний код відхиляється з причиною ALREADY_USED».</t>
+          <t>shippingFee: 0.00 від 1500 грн після знижки. F-110: безкоштовно від 2000. Для суми 1500,00–1999,99 юніт-тест shippingFee і UI-тест оформлення дадуть різні очікувані результати.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 20 реєстру</t>
+          <t>Узгодити поріг між F-110 і BL-60.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 9 реєстру (у реєстрі під ID F-110); виправлення переписано при зведенні</t>
         </is>
       </c>
     </row>
@@ -727,12 +752,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>BL-70</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -742,17 +767,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>п. 3: посилання на «Регламент програми лояльності ШопЛайн-ЛП-2025», розділ 4 — документ не входить до переліку 1.4 і команді не переданий.</t>
+          <t>п. 4, 5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>«…розділ про програму лояльності описує правила знижки за обсяг, вартості доставки і промокодів відповідно до вимог BL-50 … BL-80 цієї специфікації».</t>
+          <t>validate(code, today, subtotal): що повертається для коду, якого немає в довіднику? Що з null? «Причина відмови» — довільний рядок? Тоді assertEquals на причину не напишеш.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 8 реєстру</t>
+          <t>Причина — enum: NOT_FOUND, INVALID_LENGTH, EXPIRED, ALREADY_USED, INVALID_VALUE; null у будь-якому аргументі → IllegalArgumentException.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 7 реєстру</t>
         </is>
       </c>
     </row>
@@ -764,12 +794,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>BL-80</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -779,17 +809,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>«не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — недосяжно для повільних з'єднань (2G, супутник) і слабких пристроїв.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>«У Chrome 120+ на ПК за з'єднання 10 Мбіт/с із затримкою до 50 мс сторінка каталогу повністю завантажується (подія load) не довше ніж за 3 с; медіана з 10 вимірювань у DevTools/Lighthouse».</t>
+          <t>apply(): перевірка використання коду «у жодному іншому інтернет-магазині, зокрема сторонніх». Модуль — бібліотека без зовнішніх залежностей (2.3), API чужих магазинів немає.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 21 реєстру</t>
+          <t>Перевіряти лише замовлення «ШопЛайн».</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 20 реєстру</t>
         </is>
       </c>
     </row>
@@ -801,7 +836,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -811,22 +846,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Тестопридатність</t>
+          <t>Здійсненність</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>«Дані покупців надійно захищені, а система не містить вразливостей» — класична неперевірювана вимога: відсутність усіх вразливостей довести неможливо.</t>
+          <t>єдиний пункт</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>«Обмін даними — лише HTTPS; паролі зберігаються тільки у вигляді хешу (bcrypt або Argon2); API кабінету й рахунків-інвойсів повертає 401 без токена і 403 на запит даних іншого покупця; сканування OWASP ZAP (baseline) не виявляє вразливостей рівня High».</t>
+          <t>0,1 с «за будь-якого з'єднання і на будь-якому пристрої» — на 3G чи супутнику це фізично недосяжно.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 24 реєстру</t>
+          <t>Реальний поріг (3 с) за фіксованих умов: Chrome на ПК, 10 Мбіт/с.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 21 реєстру</t>
         </is>
       </c>
     </row>
@@ -838,7 +878,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -853,17 +893,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів» — слова-маркери «інтуїтивно», «зручно», критерію немає.</t>
+          <t>практичний тест</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>«Новий користувач без інструктажу знаходить товар пошуком і оформлює замовлення не довше ніж за 5 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5».</t>
+          <t>«не містить вразливостей» — неперевірювана вимога: тест не має результату «пройдено».</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 25 реєстру</t>
+          <t>Перелік перевірок: HTTPS, хеш паролів, 401 без токена / 403 на чужі дані, ZAP baseline без High.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 24 реєстру</t>
         </is>
       </c>
     </row>
@@ -875,7 +920,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>розд. 6, рядок після U-20, без ID</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -885,22 +930,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Простежуваність</t>
+          <t>Тестопридатність</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>п. 2: вимога «Інтерфейс коректно відображається за ширини вікна 375 пікселів…» не має ідентифікатора.</t>
+          <t>практичний тест, слова-маркери</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Присвоєно наступний вільний ID: U-30.</t>
+          <t>«інтуїтивно зрозумілим і зручним для всіх категорій користувачів» — маркери «інтуїтивно», «зручно».</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 15 реєстру</t>
+          <t>Сценарій з учасниками без інструктажу: час і кількість помилок, критерій проходження.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 25 реєстру</t>
         </is>
       </c>
     </row>
@@ -912,7 +962,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>розд. 6, рядок після U-20, без ID (→ U-30)</t>
+          <t>розд. 6, рядок після U-20, без ID</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -922,22 +972,69 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Несуперечливість</t>
+          <t>Простежуваність</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>п. 2: вимога «коректно відображається за ширини вікна 375 пікселів» суперечить 2.2 «настільні ОС; мінімальна роздільна здатність вікна 1280×800».</t>
+          <t>п. 2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2.2: «Підтримувані браузери: Chrome 120+ і Firefox 115+ на настільних ОС (вікно від 1280×800) та Chrome і Safari на мобільних пристроях (ширина вікна від 375 пікселів)» (потребує підтвердження замовником).</t>
+          <t>Рядок про ширину 375 px не має ідентифікатора — на нього неможливо послатися з тест-кейсу.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Прийнято, № 13 реєстру</t>
+          <t>Присвоїти U-30.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 15 реєстру</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>С-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>п. 3</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Посилання на «Регламент програми лояльності ШопЛайн-ЛП-2025» — у 1.4 його немає, документ не надано.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Замінити на посилання на BL-50…BL-80.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Прийнято, № 8 реєстру</t>
         </is>
       </c>
     </row>
@@ -952,11 +1049,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,17 +1119,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Знайдено (всього)</t>
+          <t>Записів в аркуші</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Прийнято до реєстру</t>
+          <t>Прийнято до реєстру як окремий дефект</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1042,7 +1139,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Відхилено</t>
+          <t>Об'єднано з іншим записом при зведенні</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1052,61 +1149,101 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— Однозначність</t>
+          <t>Відхилено на обговоренні</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— Повнота</t>
+          <t>Перекласифіковано при зведенні</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>— Несуперечливість</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>3</v>
-      </c>
+          <t>Записи за критерієм (моя оцінка)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>— Простежуваність</t>
+          <t>— Однозначність</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>— Здійсненність</t>
+          <t>— Повнота</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>— Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>— Простежуваність</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>— Здійсненність</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>— Тестопридатність</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Колонки «Що знайдено» і «Пропозиція» — формулювання до зведення; узгоджений текст дефекту і виправлення — у requirements-defects.xlsx, аркуш «Реєстр».</t>
+        </is>
       </c>
     </row>
   </sheetData>
